--- a/docs/qa/upload-templates/historical_otd_upload_template.xlsx
+++ b/docs/qa/upload-templates/historical_otd_upload_template.xlsx
@@ -131,12 +131,12 @@
     <author>IPE</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>YYYY-MM-DD</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>YYYY-MM-DD</t>
       </text>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,15 +445,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>product_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>customer_code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>planned_end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>actual_end</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delay_days</t>
         </is>
@@ -467,15 +477,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>FG-DT100</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CUST-EE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -487,15 +507,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>FG-DT250</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CUST-SEC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -507,15 +537,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>FG-DT100</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CUST-DW</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>4</v>
       </c>
     </row>
